--- a/data/trans_orig/IP07C15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C15-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22192</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27212</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>37274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>52909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61618</t>
+          <t>62320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83754</t>
+          <t>84549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>61233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84117</t>
+          <t>83136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129776</t>
+          <t>129943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161407</t>
+          <t>160299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>63977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85679</t>
+          <t>85585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80721</t>
+          <t>81926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104333</t>
+          <t>104185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151362</t>
+          <t>151136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182946</t>
+          <t>182431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48624</t>
+          <t>48438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39305</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58498</t>
+          <t>58553</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>75161</t>
+          <t>74873</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100803</t>
+          <t>101462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51311</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95466</t>
+          <t>95168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121505</t>
+          <t>121168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>90897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118130</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193121</t>
+          <t>195371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>230975</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107433</t>
+          <t>106943</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133178</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122217</t>
+          <t>122525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148924</t>
+          <t>150091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237225</t>
+          <t>235286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274964</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75337</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102630</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>133404</t>
+          <t>133901</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3231,62 +3231,62 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6178</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5589</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>51966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24589</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>28551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>45529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66171</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>89896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86835</t>
+          <t>87096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111134</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160166</t>
+          <t>160406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194857</t>
+          <t>193065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68921</t>
+          <t>68888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92041</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73370</t>
+          <t>74245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96506</t>
+          <t>97460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149124</t>
+          <t>149171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182994</t>
+          <t>181425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>29541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48282</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>44805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87568</t>
+          <t>87475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37091</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>42240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59729</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34909</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118201</t>
+          <t>117926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145946</t>
+          <t>146257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126032</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154576</t>
+          <t>155017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250190</t>
+          <t>251055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291622</t>
+          <t>290972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103897</t>
+          <t>103404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131432</t>
+          <t>131845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113221</t>
+          <t>112581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>142107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224819</t>
+          <t>224334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266603</t>
+          <t>263905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>47712</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70896</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61385</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93029</t>
+          <t>92629</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>124462</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26068</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28938</t>
+          <t>28397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43826</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70698</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94607</t>
+          <t>94870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73785</t>
+          <t>74105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98828</t>
+          <t>99028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150726</t>
+          <t>150773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185825</t>
+          <t>185840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101847</t>
+          <t>102111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128022</t>
+          <t>128675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>95314</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122147</t>
+          <t>121453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205397</t>
+          <t>206225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242911</t>
+          <t>241363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>34754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>54114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42177</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>62703</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88922</t>
+          <t>89810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>32223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>38935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46502</t>
+          <t>47140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66195</t>
+          <t>67034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39376</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>54991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75320</t>
+          <t>75289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103515</t>
+          <t>103850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133354</t>
+          <t>132908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108236</t>
+          <t>111280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>223257</t>
+          <t>223750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265214</t>
+          <t>263444</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>145558</t>
+          <t>143869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175350</t>
+          <t>174849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>148698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182542</t>
+          <t>179339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>305288</t>
+          <t>302145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>346157</t>
+          <t>346191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>49761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123467</t>
+          <t>126684</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -9149,82 +9149,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t>615</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5858</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>28258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63377</t>
+          <t>62537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75936</t>
+          <t>76381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112059</t>
+          <t>116877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107456</t>
+          <t>110600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167027</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,85%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73940</t>
+          <t>74403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121623</t>
+          <t>119101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63658</t>
+          <t>60452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93782</t>
+          <t>94489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145656</t>
+          <t>143431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217893</t>
+          <t>218024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>25775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32086</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63825</t>
+          <t>64513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>25635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60355</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46697</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>90425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114784</t>
+          <t>113396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153356</t>
+          <t>153859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167640</t>
+          <t>167157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232476</t>
+          <t>229081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93164</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152018</t>
+          <t>148821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83358</t>
+          <t>84163</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>118129</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186849</t>
+          <t>187706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>267336</t>
+          <t>260105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75240</t>
+          <t>74204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
